--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="235">
   <si>
     <t>Term</t>
   </si>
@@ -97,7 +97,7 @@
     <t>Chair release</t>
   </si>
   <si>
-    <t>SYNTHETIC: AY, one row per spread term</t>
+    <t>Split over fall and spring</t>
   </si>
   <si>
     <t>SP</t>
@@ -106,390 +106,540 @@
     <t>SP-Full</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Ben Sample</t>
+  </si>
+  <si>
+    <t>Research release</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Eli Specimen</t>
+  </si>
+  <si>
+    <t>Advising coordinator</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Ben Sample</t>
-  </si>
-  <si>
-    <t>Sabbatical</t>
-  </si>
-  <si>
-    <t>DATA</t>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Data Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
   </si>
   <si>
     <t>301</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>TR</t>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Data Science Capstone</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>14:10:00 - 15:50:00</t>
   </si>
   <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>FA-First</t>
+  </si>
+  <si>
+    <t>Data Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>FA-Second</t>
+  </si>
+  <si>
+    <t>Data Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as STAT 385</t>
+  </si>
+  <si>
+    <t>STAT 385</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>MATH</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>MTWRF</t>
+  </si>
+  <si>
+    <t>09:00:00 - 11:30:00</t>
+  </si>
+  <si>
+    <t>NH 101</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Mathematics and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>Calculus I</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>SU-Second</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Calculus I (second semester)</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Calculus II</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Linear Algebra</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>Multivariable Calculus</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>Discrete Mathematics</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
     <t>NH 104</t>
   </si>
   <si>
-    <t>Topics</t>
-  </si>
-  <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
-    <t>STAT 305, MATH 307</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>MWF</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Optimization</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>STAT 385</t>
-  </si>
-  <si>
-    <t>EDUC</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1.8</t>
+    <t>Real Analysis I</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Real Analysis II</t>
+  </si>
+  <si>
+    <t>STAT</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Sports Analytics</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>Introduction to Statistics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-First</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>Statistical Methods</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH143-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH143-B</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH162-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH231-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH256-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH351-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT143-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT243-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT343-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA202-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA380-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA381-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA385-A</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-MATH110-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-STAT130-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH144-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH162-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH232-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH352-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT143-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT244-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DATA301-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DATA302-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-MATH143-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-STAT143-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
   </si>
   <si>
     <t>Off Campus</t>
   </si>
   <si>
-    <t>Internship</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Might be 1.8 hours</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>10:15:00 - 11:20:00</t>
-  </si>
-  <si>
-    <t>NH 101</t>
-  </si>
-  <si>
-    <t>Calculus</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MW
-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:15:00 - 10:20:00
-10:20:00 - 11:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 101
-NH 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65
-50</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>Ada Example, Ben Sample</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MWF
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:00:00 - 10:05:00
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 105
-Online</t>
-  </si>
-  <si>
-    <t>SU-Full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65
-</t>
-  </si>
-  <si>
-    <t>Summer Topics</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR
-TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:20:00 - 12:00:00
-11:20:00 - 13:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 1
-NH 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100
-100</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>R1-FA-MATH101-A</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>R1-SP-MATH102-A</t>
-  </si>
-  <si>
-    <t>Ada Example (3), Ben Sample (1)</t>
-  </si>
-  <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>R1-FA-STAT201-A</t>
-  </si>
-  <si>
-    <t>NH 1</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>NH 2</t>
-  </si>
-  <si>
-    <t>R1-FA-EDUC346-J</t>
-  </si>
-  <si>
-    <t>R1-FA-DATA385-A</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>R1-SP-DATA301-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>R1-SU-MATH150-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
     <t>Fall</t>
   </si>
   <si>
-    <t>WI</t>
-  </si>
-  <si>
     <t>Winter Intensive</t>
   </si>
   <si>
@@ -505,24 +655,15 @@
     <t>Full term</t>
   </si>
   <si>
-    <t>First</t>
-  </si>
-  <si>
     <t>First half</t>
   </si>
   <si>
-    <t>Second</t>
-  </si>
-  <si>
     <t>Second half</t>
   </si>
   <si>
     <t>Intensive A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Intensive B</t>
   </si>
   <si>
@@ -556,7 +697,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:15:43</t>
+    <t>10:29:00</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -619,12 +760,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -964,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -977,12 +1115,12 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="31" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1211,114 +1349,114 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5">
-        <v>100</v>
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="s">
         <v>19</v>
       </c>
       <c r="R5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>65</v>
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="s">
         <v>19</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1326,28 +1464,28 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -1355,23 +1493,23 @@
       <c r="K7" t="s">
         <v>23</v>
       </c>
-      <c r="L7" t="s">
-        <v>19</v>
+      <c r="L7">
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="R7" t="s">
         <v>19</v>
@@ -1379,52 +1517,52 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L8">
         <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="s">
         <v>19</v>
@@ -1438,28 +1576,28 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>67</v>
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -1467,20 +1605,20 @@
       <c r="K9" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>68</v>
+      <c r="L9">
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="O9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="s">
         <v>19</v>
@@ -1491,55 +1629,55 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M10" t="s">
-        <v>79</v>
-      </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="R10" t="s">
         <v>19</v>
@@ -1550,54 +1688,1174 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12">
+        <v>65</v>
+      </c>
+      <c r="M12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13">
+        <v>150</v>
+      </c>
+      <c r="M13" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
         <v>80</v>
       </c>
-      <c r="C11" t="s">
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14">
+        <v>65</v>
+      </c>
+      <c r="M14" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="N14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="L15">
+        <v>150</v>
+      </c>
+      <c r="M15" t="s">
+        <v>81</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" t="s">
         <v>84</v>
       </c>
-      <c r="J11" t="s">
+      <c r="R15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
         <v>22</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K16" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="L16">
+        <v>65</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17">
+        <v>65</v>
+      </c>
+      <c r="M17" t="s">
+        <v>88</v>
+      </c>
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
         <v>86</v>
       </c>
-      <c r="N11" t="s">
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18">
+        <v>65</v>
+      </c>
+      <c r="M18" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
         <v>47</v>
       </c>
-      <c r="O11" t="s">
+      <c r="H19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" t="s">
         <v>39</v>
       </c>
-      <c r="P11" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>19</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20" t="s">
+        <v>95</v>
+      </c>
+      <c r="N20" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N21" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22">
+        <v>65</v>
+      </c>
+      <c r="M22" t="s">
+        <v>100</v>
+      </c>
+      <c r="N22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>103</v>
+      </c>
+      <c r="N23" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>19</v>
+      </c>
+      <c r="R23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24" t="s">
+        <v>105</v>
+      </c>
+      <c r="N24" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>19</v>
+      </c>
+      <c r="R24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25">
+        <v>150</v>
+      </c>
+      <c r="M25" t="s">
+        <v>110</v>
+      </c>
+      <c r="N25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O25" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>19</v>
+      </c>
+      <c r="R25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>112</v>
+      </c>
+      <c r="N26" t="s">
+        <v>113</v>
+      </c>
+      <c r="O26" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>19</v>
+      </c>
+      <c r="R26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N27" t="s">
+        <v>113</v>
+      </c>
+      <c r="O27" t="s">
+        <v>44</v>
+      </c>
+      <c r="P27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>19</v>
+      </c>
+      <c r="R27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28">
+        <v>150</v>
+      </c>
+      <c r="M28" t="s">
+        <v>112</v>
+      </c>
+      <c r="N28" t="s">
+        <v>113</v>
+      </c>
+      <c r="O28" t="s">
+        <v>44</v>
+      </c>
+      <c r="P28" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>116</v>
+      </c>
+      <c r="R28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29" t="s">
+        <v>118</v>
+      </c>
+      <c r="N29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" t="s">
+        <v>44</v>
+      </c>
+      <c r="P29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>19</v>
+      </c>
+      <c r="R29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30" t="s">
+        <v>120</v>
+      </c>
+      <c r="N30" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" t="s">
+        <v>44</v>
+      </c>
+      <c r="P30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>19</v>
+      </c>
+      <c r="R30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
+        <v>109</v>
+      </c>
+      <c r="J31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31" t="s">
+        <v>122</v>
+      </c>
+      <c r="N31" t="s">
+        <v>123</v>
+      </c>
+      <c r="O31" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1609,42 +2867,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="9" max="9" width="31" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1668,22 +2926,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1692,10 +2950,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1704,21 +2962,21 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -1727,16 +2985,16 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1748,22 +3006,22 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
         <v>19</v>
@@ -1772,7 +3030,7 @@
         <v>19</v>
       </c>
       <c r="U2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V2" t="s">
         <v>19</v>
@@ -1786,31 +3044,31 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1822,22 +3080,22 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="N3" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
         <v>19</v>
@@ -1846,7 +3104,7 @@
         <v>19</v>
       </c>
       <c r="U3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -1860,31 +3118,31 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1896,22 +3154,22 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="R4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S4" t="s">
         <v>19</v>
@@ -1920,7 +3178,7 @@
         <v>19</v>
       </c>
       <c r="U4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
         <v>19</v>
@@ -1934,13 +3192,13 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1949,16 +3207,16 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1970,22 +3228,22 @@
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S5" t="s">
         <v>19</v>
@@ -1994,7 +3252,7 @@
         <v>19</v>
       </c>
       <c r="U5" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="V5" t="s">
         <v>19</v>
@@ -2008,13 +3266,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2023,16 +3281,16 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2044,22 +3302,22 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="O6">
+        <v>65</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" t="s">
         <v>100</v>
       </c>
-      <c r="P6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>86</v>
-      </c>
       <c r="R6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S6" t="s">
         <v>19</v>
@@ -2068,7 +3326,7 @@
         <v>19</v>
       </c>
       <c r="U6" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="V6" t="s">
         <v>19</v>
@@ -2082,13 +3340,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2097,43 +3355,43 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="J7">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" t="s">
-        <v>19</v>
+        <v>147</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="S7" t="s">
         <v>19</v>
@@ -2142,10 +3400,10 @@
         <v>19</v>
       </c>
       <c r="U7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="V7" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="W7" t="s">
         <v>19</v>
@@ -2156,13 +3414,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -2171,16 +3429,16 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2192,31 +3450,31 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N8" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>112</v>
+      </c>
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s">
         <v>45</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>46</v>
-      </c>
-      <c r="R8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>40</v>
       </c>
       <c r="V8" t="s">
         <v>19</v>
@@ -2230,31 +3488,31 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
         <v>33</v>
-      </c>
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" t="s">
-        <v>30</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2266,22 +3524,22 @@
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="Q9" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S9" t="s">
         <v>19</v>
@@ -2290,7 +3548,7 @@
         <v>19</v>
       </c>
       <c r="U9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V9" t="s">
         <v>19</v>
@@ -2304,58 +3562,58 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="R10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S10" t="s">
         <v>19</v>
@@ -2364,7 +3622,7 @@
         <v>19</v>
       </c>
       <c r="U10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V10" t="s">
         <v>19</v>
@@ -2378,75 +3636,1185 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>145</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>42</v>
+      </c>
+      <c r="R11" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U11" t="s">
+        <v>45</v>
+      </c>
+      <c r="V11" t="s">
+        <v>19</v>
+      </c>
+      <c r="W11" t="s">
+        <v>19</v>
+      </c>
+      <c r="X11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
+        <v>147</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12" t="s">
         <v>58</v>
       </c>
-      <c r="G11" t="s">
+      <c r="R12" t="s">
+        <v>44</v>
+      </c>
+      <c r="S12" t="s">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>59</v>
+      </c>
+      <c r="W12" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s">
+        <v>147</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" t="s">
+        <v>44</v>
+      </c>
+      <c r="S13" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>64</v>
+      </c>
+      <c r="W13" t="s">
+        <v>19</v>
+      </c>
+      <c r="X13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" t="s">
+        <v>47</v>
+      </c>
+      <c r="N14" t="s">
+        <v>156</v>
+      </c>
+      <c r="O14">
+        <v>65</v>
+      </c>
+      <c r="P14" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" t="s">
+        <v>67</v>
+      </c>
+      <c r="W14" t="s">
+        <v>19</v>
+      </c>
+      <c r="X14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" t="s">
         <v>72</v>
       </c>
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11">
+      <c r="N15" t="s">
+        <v>158</v>
+      </c>
+      <c r="O15">
+        <v>150</v>
+      </c>
+      <c r="P15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s">
+        <v>45</v>
+      </c>
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
+        <v>19</v>
+      </c>
+      <c r="X15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" t="s">
+        <v>160</v>
+      </c>
+      <c r="O16">
+        <v>150</v>
+      </c>
+      <c r="P16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s">
+        <v>45</v>
+      </c>
+      <c r="V16" t="s">
+        <v>19</v>
+      </c>
+      <c r="W16" t="s">
+        <v>19</v>
+      </c>
+      <c r="X16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" t="s">
+        <v>47</v>
+      </c>
+      <c r="N17" t="s">
+        <v>138</v>
+      </c>
+      <c r="O17">
+        <v>65</v>
+      </c>
+      <c r="P17" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" t="s">
+        <v>44</v>
+      </c>
+      <c r="S17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s">
+        <v>45</v>
+      </c>
+      <c r="V17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" t="s">
+        <v>138</v>
+      </c>
+      <c r="O18">
+        <v>65</v>
+      </c>
+      <c r="P18" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>91</v>
+      </c>
+      <c r="R18" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
+        <v>45</v>
+      </c>
+      <c r="V18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W18" t="s">
+        <v>19</v>
+      </c>
+      <c r="X18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" t="s">
+        <v>39</v>
+      </c>
+      <c r="N19" t="s">
+        <v>143</v>
+      </c>
+      <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" t="s">
+        <v>44</v>
+      </c>
+      <c r="S19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
+        <v>45</v>
+      </c>
+      <c r="V19" t="s">
+        <v>19</v>
+      </c>
+      <c r="W19" t="s">
+        <v>19</v>
+      </c>
+      <c r="X19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>105</v>
+      </c>
+      <c r="R20" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" t="s">
+        <v>19</v>
+      </c>
+      <c r="T20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
+        <v>45</v>
+      </c>
+      <c r="V20" t="s">
+        <v>19</v>
+      </c>
+      <c r="W20" t="s">
+        <v>19</v>
+      </c>
+      <c r="X20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" t="s">
+        <v>47</v>
+      </c>
+      <c r="N21" t="s">
+        <v>149</v>
+      </c>
+      <c r="O21">
+        <v>65</v>
+      </c>
+      <c r="P21" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>112</v>
+      </c>
+      <c r="R21" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s">
+        <v>45</v>
+      </c>
+      <c r="V21" t="s">
+        <v>19</v>
+      </c>
+      <c r="W21" t="s">
+        <v>19</v>
+      </c>
+      <c r="X21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" t="s">
+        <v>39</v>
+      </c>
+      <c r="N22" t="s">
+        <v>143</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>120</v>
+      </c>
+      <c r="R22" t="s">
+        <v>44</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
+        <v>45</v>
+      </c>
+      <c r="V22" t="s">
+        <v>19</v>
+      </c>
+      <c r="W22" t="s">
+        <v>19</v>
+      </c>
+      <c r="X22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23" t="s">
+        <v>156</v>
+      </c>
+      <c r="O23">
+        <v>65</v>
+      </c>
+      <c r="P23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>49</v>
+      </c>
+      <c r="R23" t="s">
+        <v>44</v>
+      </c>
+      <c r="S23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T23" t="s">
+        <v>19</v>
+      </c>
+      <c r="U23" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" t="s">
+        <v>19</v>
+      </c>
+      <c r="W23" t="s">
+        <v>19</v>
+      </c>
+      <c r="X23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
+        <v>39</v>
+      </c>
+      <c r="N24" t="s">
+        <v>140</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>52</v>
+      </c>
+      <c r="R24" t="s">
+        <v>44</v>
+      </c>
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" t="s">
+        <v>45</v>
+      </c>
+      <c r="V24" t="s">
+        <v>19</v>
+      </c>
+      <c r="W24" t="s">
+        <v>19</v>
+      </c>
+      <c r="X24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25">
         <v>2</v>
       </c>
-      <c r="K11">
+      <c r="K25">
         <v>2</v>
       </c>
-      <c r="L11" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="L25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" t="s">
+        <v>158</v>
+      </c>
+      <c r="O25">
+        <v>150</v>
+      </c>
+      <c r="P25" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>81</v>
+      </c>
+      <c r="R25" t="s">
+        <v>44</v>
+      </c>
+      <c r="S25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T25" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" t="s">
+        <v>45</v>
+      </c>
+      <c r="V25" t="s">
+        <v>84</v>
+      </c>
+      <c r="W25" t="s">
+        <v>19</v>
+      </c>
+      <c r="X25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
         <v>79</v>
       </c>
-      <c r="R11" t="s">
-        <v>39</v>
-      </c>
-      <c r="S11" t="s">
-        <v>19</v>
-      </c>
-      <c r="T11" t="s">
-        <v>19</v>
-      </c>
-      <c r="U11" t="s">
-        <v>40</v>
-      </c>
-      <c r="V11" t="s">
-        <v>19</v>
-      </c>
-      <c r="W11" t="s">
-        <v>19</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" t="s">
+        <v>113</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" t="s">
+        <v>72</v>
+      </c>
+      <c r="N26" t="s">
+        <v>158</v>
+      </c>
+      <c r="O26">
+        <v>150</v>
+      </c>
+      <c r="P26" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>112</v>
+      </c>
+      <c r="R26" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" t="s">
+        <v>19</v>
+      </c>
+      <c r="T26" t="s">
+        <v>19</v>
+      </c>
+      <c r="U26" t="s">
+        <v>115</v>
+      </c>
+      <c r="V26" t="s">
+        <v>116</v>
+      </c>
+      <c r="W26" t="s">
+        <v>19</v>
+      </c>
+      <c r="X26" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2458,17 +4826,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2479,35 +4847,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2518,31 +4864,30 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -2550,7 +4895,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -2559,7 +4904,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2570,7 +4915,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
@@ -2582,9 +4927,29 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2596,11 +4961,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
@@ -2609,74 +4974,261 @@
     <col min="9" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="14" width="6" customWidth="1"/>
+    <col min="12" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="4" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>193</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>195</v>
+      </c>
+      <c r="K4" t="s">
+        <v>196</v>
+      </c>
+      <c r="L4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M4" t="s">
+        <v>193</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2698,27 +5250,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -2738,7 +5290,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
@@ -2758,10 +5310,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -2778,10 +5330,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -2798,10 +5350,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -2824,7 +5376,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -2841,10 +5393,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -2864,7 +5416,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -2881,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
@@ -2898,13 +5450,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
@@ -2918,13 +5470,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -2938,13 +5490,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -2958,13 +5510,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -2978,13 +5530,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -2998,13 +5550,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -3018,13 +5570,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
@@ -3038,16 +5590,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3073,39 +5625,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -3113,7 +5665,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -3121,23 +5673,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -3145,7 +5697,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="236">
   <si>
     <t>Term</t>
   </si>
@@ -697,7 +697,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:29:00</t>
+    <t>22:57:57</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Default Department</t>
   </si>
   <si>
     <t>Version</t>
@@ -5616,7 +5619,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5703,6 +5706,14 @@
         <v>19</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -124,10 +124,10 @@
     <t>Advising coordinator</t>
   </si>
   <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>202</t>
+    <t>AMUS</t>
+  </si>
+  <si>
+    <t>112</t>
   </si>
   <si>
     <t>A</t>
@@ -136,261 +136,261 @@
     <t>4</t>
   </si>
   <si>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>NH 101</t>
+  </si>
+  <si>
+    <t>Musical Patterns I</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MTWRF</t>
+  </si>
+  <si>
+    <t>09:00:00 - 11:30:00</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>SU-Second</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Musical Patterns I (second semester)</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
     <t>TR</t>
   </si>
   <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>SU-First</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
     <t>08:00:00 - 09:40:00</t>
   </si>
   <si>
     <t>SB 110</t>
   </si>
   <si>
-    <t>Data Computing</t>
+    <t>Information Computing</t>
   </si>
   <si>
     <t>Fay Mockson</t>
   </si>
   <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>MWF</t>
+    <t>306</t>
   </si>
   <si>
     <t>11:00:00 - 12:05:00</t>
   </si>
   <si>
-    <t>Machine Learning</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Data Science Capstone</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>First</t>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
   </si>
   <si>
     <t>FA-First</t>
   </si>
   <si>
-    <t>Data Ethics</t>
+    <t>Information Ethics</t>
   </si>
   <si>
     <t>First half of the term</t>
   </si>
   <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Second</t>
+    <t>378</t>
   </si>
   <si>
     <t>FA-Second</t>
   </si>
   <si>
-    <t>Data Visualization</t>
+    <t>Information Visualization</t>
   </si>
   <si>
     <t>Second half of the term</t>
   </si>
   <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as STAT 385</t>
-  </si>
-  <si>
-    <t>STAT 385</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>MTWRF</t>
-  </si>
-  <si>
-    <t>09:00:00 - 11:30:00</t>
-  </si>
-  <si>
-    <t>NH 101</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Mathematics and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>09:15:00 - 10:20:00</t>
-  </si>
-  <si>
-    <t>Calculus I</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>SU-Second</t>
-  </si>
-  <si>
-    <t>Summer session II</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:20:00</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Calculus I (second semester)</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>Calculus II</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>Multivariable Calculus</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>Discrete Mathematics</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Real Analysis I</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Real Analysis II</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Sports Analytics</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>Introduction to Statistics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>SU-First</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
     <t>SectionId</t>
   </si>
   <si>
@@ -427,7 +427,7 @@
     <t>EnrollmentDay10</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-A</t>
+    <t>AY25-FA-AMUS112-A</t>
   </si>
   <si>
     <t>AY25</t>
@@ -436,100 +436,100 @@
     <t>09:15</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-B</t>
+    <t>AY25-FA-AMUS112-B</t>
   </si>
   <si>
     <t>12:15</t>
   </si>
   <si>
-    <t>AY25-FA-MATH162-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-MATH231-A</t>
+    <t>AY25-FA-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
   </si>
   <si>
     <t>10:20</t>
   </si>
   <si>
-    <t>AY25-FA-MATH256-A</t>
+    <t>AY25-FA-AMUS203-A</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>AY25-FA-MATH351-A</t>
+    <t>AY25-FA-AMUS368-A</t>
   </si>
   <si>
     <t>14:10</t>
   </si>
   <si>
-    <t>AY25-FA-STAT143-A</t>
+    <t>AY25-FA-BHAV112-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>AY25-FA-STAT243-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-STAT343-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA202-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA380-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA381-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA385-A</t>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>AY25-WI-MATH110-A</t>
+    <t>AY25-WI-AMUS181-A</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>AY25-WI-STAT130-A</t>
+    <t>AY25-WI-BHAV121-A</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>AY25-SP-MATH144-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH162-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH232-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH352-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT143-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT244-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DATA301-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DATA302-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-MATH143-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-STAT143-A</t>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -691,13 +691,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-03</t>
+    <t>2026-10-04</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>22:57:57</t>
+    <t>08:26:04</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1118,7 +1118,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="38" customWidth="1"/>
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1497,19 +1497,19 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
         <v>42</v>
       </c>
       <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
         <v>43</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>44</v>
-      </c>
-      <c r="P7" t="s">
-        <v>45</v>
       </c>
       <c r="Q7" t="s">
         <v>19</v>
@@ -1520,22 +1520,22 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>47</v>
@@ -1547,28 +1547,28 @@
         <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K8" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
         <v>43</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>44</v>
       </c>
-      <c r="P8" t="s">
-        <v>45</v>
-      </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="R8" t="s">
         <v>19</v>
@@ -1576,16 +1576,16 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -1597,7 +1597,7 @@
         <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
         <v>41</v>
@@ -1606,22 +1606,22 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="N9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
         <v>43</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>44</v>
-      </c>
-      <c r="P9" t="s">
-        <v>45</v>
       </c>
       <c r="Q9" t="s">
         <v>19</v>
@@ -1632,55 +1632,55 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
         <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
         <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" t="s">
         <v>43</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>44</v>
       </c>
-      <c r="P10" t="s">
-        <v>45</v>
-      </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="R10" t="s">
         <v>19</v>
@@ -1694,49 +1694,49 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
         <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J11" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
         <v>43</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>44</v>
       </c>
-      <c r="P11" t="s">
-        <v>45</v>
-      </c>
       <c r="Q11" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
         <v>19</v>
@@ -1744,13 +1744,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
@@ -1762,51 +1762,51 @@
         <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
         <v>43</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>44</v>
       </c>
-      <c r="P12" t="s">
-        <v>45</v>
-      </c>
       <c r="Q12" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="R12" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
         <v>37</v>
@@ -1818,37 +1818,37 @@
         <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
         <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="O13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" t="s">
         <v>44</v>
       </c>
-      <c r="P13" t="s">
-        <v>45</v>
-      </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="R13" t="s">
         <v>19</v>
@@ -1859,10 +1859,10 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1874,13 +1874,13 @@
         <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -1892,16 +1892,16 @@
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="N14" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="O14" t="s">
+        <v>43</v>
+      </c>
+      <c r="P14" t="s">
         <v>44</v>
-      </c>
-      <c r="P14" t="s">
-        <v>45</v>
       </c>
       <c r="Q14" t="s">
         <v>19</v>
@@ -1912,55 +1912,55 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15" t="s">
         <v>72</v>
       </c>
-      <c r="H15" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" t="s">
-        <v>83</v>
-      </c>
-      <c r="L15">
-        <v>150</v>
-      </c>
-      <c r="M15" t="s">
-        <v>81</v>
-      </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="O15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P15" t="s">
         <v>44</v>
       </c>
-      <c r="P15" t="s">
-        <v>45</v>
-      </c>
       <c r="Q15" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="R15" t="s">
         <v>19</v>
@@ -1968,16 +1968,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
@@ -1986,34 +1986,34 @@
         <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L16">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="N16" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="O16" t="s">
+        <v>43</v>
+      </c>
+      <c r="P16" t="s">
         <v>44</v>
-      </c>
-      <c r="P16" t="s">
-        <v>45</v>
       </c>
       <c r="Q16" t="s">
         <v>19</v>
@@ -2024,13 +2024,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -2042,34 +2042,34 @@
         <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
       </c>
       <c r="K17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="N17" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="O17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" t="s">
         <v>44</v>
-      </c>
-      <c r="P17" t="s">
-        <v>45</v>
       </c>
       <c r="Q17" t="s">
         <v>19</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>37</v>
@@ -2098,34 +2098,34 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L18">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
       </c>
       <c r="O18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" t="s">
         <v>44</v>
-      </c>
-      <c r="P18" t="s">
-        <v>45</v>
       </c>
       <c r="Q18" t="s">
         <v>19</v>
@@ -2136,13 +2136,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -2154,34 +2154,34 @@
         <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="O19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" t="s">
         <v>44</v>
-      </c>
-      <c r="P19" t="s">
-        <v>45</v>
       </c>
       <c r="Q19" t="s">
         <v>19</v>
@@ -2192,13 +2192,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>37</v>
@@ -2213,31 +2213,31 @@
         <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
       </c>
       <c r="K20" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="N20" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O20" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" t="s">
         <v>44</v>
-      </c>
-      <c r="P20" t="s">
-        <v>45</v>
       </c>
       <c r="Q20" t="s">
         <v>19</v>
@@ -2248,55 +2248,55 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="N21" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P21" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="Q21" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="R21" t="s">
         <v>19</v>
@@ -2304,13 +2304,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
@@ -2325,31 +2325,31 @@
         <v>47</v>
       </c>
       <c r="H22" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
       </c>
       <c r="K22" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="L22">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="O22" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" t="s">
         <v>44</v>
-      </c>
-      <c r="P22" t="s">
-        <v>45</v>
       </c>
       <c r="Q22" t="s">
         <v>19</v>
@@ -2363,10 +2363,10 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -2378,13 +2378,13 @@
         <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I23" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -2396,16 +2396,16 @@
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="O23" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" t="s">
         <v>44</v>
-      </c>
-      <c r="P23" t="s">
-        <v>45</v>
       </c>
       <c r="Q23" t="s">
         <v>19</v>
@@ -2419,10 +2419,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -2434,13 +2434,13 @@
         <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -2452,16 +2452,16 @@
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
+        <v>43</v>
+      </c>
+      <c r="P24" t="s">
         <v>44</v>
-      </c>
-      <c r="P24" t="s">
-        <v>45</v>
       </c>
       <c r="Q24" t="s">
         <v>19</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
@@ -2490,34 +2490,34 @@
         <v>38</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="L25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O25" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25" t="s">
         <v>44</v>
-      </c>
-      <c r="P25" t="s">
-        <v>45</v>
       </c>
       <c r="Q25" t="s">
         <v>19</v>
@@ -2531,10 +2531,10 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
@@ -2546,13 +2546,13 @@
         <v>38</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -2561,19 +2561,19 @@
         <v>23</v>
       </c>
       <c r="L26">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="O26" t="s">
+        <v>43</v>
+      </c>
+      <c r="P26" t="s">
         <v>44</v>
-      </c>
-      <c r="P26" t="s">
-        <v>45</v>
       </c>
       <c r="Q26" t="s">
         <v>19</v>
@@ -2584,13 +2584,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>37</v>
@@ -2602,93 +2602,93 @@
         <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L27">
         <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N27" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="O27" t="s">
+        <v>43</v>
+      </c>
+      <c r="P27" t="s">
         <v>44</v>
       </c>
-      <c r="P27" t="s">
-        <v>45</v>
-      </c>
       <c r="Q27" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="R27" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="K28" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="L28">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="O28" t="s">
+        <v>43</v>
+      </c>
+      <c r="P28" t="s">
         <v>44</v>
       </c>
-      <c r="P28" t="s">
-        <v>115</v>
-      </c>
       <c r="Q28" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="R28" t="s">
         <v>19</v>
@@ -2696,13 +2696,13 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>37</v>
@@ -2714,34 +2714,34 @@
         <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H29" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="O29" t="s">
+        <v>43</v>
+      </c>
+      <c r="P29" t="s">
         <v>44</v>
-      </c>
-      <c r="P29" t="s">
-        <v>45</v>
       </c>
       <c r="Q29" t="s">
         <v>19</v>
@@ -2752,55 +2752,55 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="O30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P30" t="s">
         <v>44</v>
       </c>
-      <c r="P30" t="s">
-        <v>45</v>
-      </c>
       <c r="Q30" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="R30" t="s">
         <v>19</v>
@@ -2811,34 +2811,34 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J31" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K31" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -2847,16 +2847,16 @@
         <v>122</v>
       </c>
       <c r="N31" t="s">
+        <v>106</v>
+      </c>
+      <c r="O31" t="s">
+        <v>43</v>
+      </c>
+      <c r="P31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q31" t="s">
         <v>123</v>
-      </c>
-      <c r="O31" t="s">
-        <v>44</v>
-      </c>
-      <c r="P31" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>19</v>
       </c>
       <c r="R31" t="s">
         <v>19</v>
@@ -2887,7 +2887,7 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
@@ -2988,10 +2988,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
@@ -3009,7 +3009,7 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
         <v>138</v>
@@ -3018,22 +3018,22 @@
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
         <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" t="s">
-        <v>45</v>
       </c>
       <c r="V2" t="s">
         <v>19</v>
@@ -3062,13 +3062,13 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
@@ -3083,7 +3083,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
         <v>140</v>
@@ -3092,22 +3092,22 @@
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" t="s">
         <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3" t="s">
-        <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -3136,10 +3136,10 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -3157,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
         <v>140</v>
@@ -3166,22 +3166,22 @@
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="Q4" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="R4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" t="s">
         <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" t="s">
-        <v>19</v>
-      </c>
-      <c r="U4" t="s">
-        <v>45</v>
       </c>
       <c r="V4" t="s">
         <v>19</v>
@@ -3210,16 +3210,16 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3231,7 +3231,7 @@
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
         <v>143</v>
@@ -3240,22 +3240,22 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" t="s">
         <v>44</v>
-      </c>
-      <c r="S5" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U5" t="s">
-        <v>45</v>
       </c>
       <c r="V5" t="s">
         <v>19</v>
@@ -3284,16 +3284,16 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
         <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3305,7 +3305,7 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N6" t="s">
         <v>145</v>
@@ -3314,22 +3314,22 @@
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="R6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" t="s">
         <v>44</v>
-      </c>
-      <c r="S6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T6" t="s">
-        <v>19</v>
-      </c>
-      <c r="U6" t="s">
-        <v>45</v>
       </c>
       <c r="V6" t="s">
         <v>19</v>
@@ -3358,16 +3358,16 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s">
         <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3379,7 +3379,7 @@
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
         <v>147</v>
@@ -3388,22 +3388,22 @@
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="R7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T7" t="s">
+        <v>19</v>
+      </c>
+      <c r="U7" t="s">
         <v>44</v>
-      </c>
-      <c r="S7" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" t="s">
-        <v>19</v>
-      </c>
-      <c r="U7" t="s">
-        <v>45</v>
       </c>
       <c r="V7" t="s">
         <v>19</v>
@@ -3432,16 +3432,16 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3453,7 +3453,7 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
         <v>149</v>
@@ -3462,22 +3462,22 @@
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q8" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="R8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s">
         <v>44</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>45</v>
       </c>
       <c r="V8" t="s">
         <v>19</v>
@@ -3506,10 +3506,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s">
         <v>37</v>
@@ -3527,7 +3527,7 @@
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N9" t="s">
         <v>143</v>
@@ -3536,22 +3536,22 @@
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q9" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="R9" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" t="s">
         <v>44</v>
-      </c>
-      <c r="S9" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U9" t="s">
-        <v>45</v>
       </c>
       <c r="V9" t="s">
         <v>19</v>
@@ -3580,16 +3580,16 @@
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3601,7 +3601,7 @@
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N10" t="s">
         <v>140</v>
@@ -3610,22 +3610,22 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q10" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="R10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U10" t="s">
         <v>44</v>
-      </c>
-      <c r="S10" t="s">
-        <v>19</v>
-      </c>
-      <c r="T10" t="s">
-        <v>19</v>
-      </c>
-      <c r="U10" t="s">
-        <v>45</v>
       </c>
       <c r="V10" t="s">
         <v>19</v>
@@ -3654,16 +3654,16 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3675,7 +3675,7 @@
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N11" t="s">
         <v>145</v>
@@ -3684,22 +3684,22 @@
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="R11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U11" t="s">
         <v>44</v>
-      </c>
-      <c r="S11" t="s">
-        <v>19</v>
-      </c>
-      <c r="T11" t="s">
-        <v>19</v>
-      </c>
-      <c r="U11" t="s">
-        <v>45</v>
       </c>
       <c r="V11" t="s">
         <v>19</v>
@@ -3725,19 +3725,19 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
         <v>37</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -3749,7 +3749,7 @@
         <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N12" t="s">
         <v>147</v>
@@ -3758,25 +3758,25 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="R12" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" t="s">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s">
         <v>44</v>
       </c>
-      <c r="S12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T12" t="s">
-        <v>19</v>
-      </c>
-      <c r="U12" t="s">
-        <v>45</v>
-      </c>
       <c r="V12" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="W12" t="s">
         <v>19</v>
@@ -3799,19 +3799,19 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H13" t="s">
         <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -3823,7 +3823,7 @@
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N13" t="s">
         <v>147</v>
@@ -3832,25 +3832,25 @@
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q13" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="R13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s">
         <v>44</v>
       </c>
-      <c r="S13" t="s">
-        <v>19</v>
-      </c>
-      <c r="T13" t="s">
-        <v>19</v>
-      </c>
-      <c r="U13" t="s">
-        <v>45</v>
-      </c>
       <c r="V13" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="W13" t="s">
         <v>19</v>
@@ -3876,16 +3876,16 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="H14" t="s">
         <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -3897,7 +3897,7 @@
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N14" t="s">
         <v>156</v>
@@ -3906,25 +3906,25 @@
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="R14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S14" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s">
         <v>44</v>
       </c>
-      <c r="S14" t="s">
-        <v>19</v>
-      </c>
-      <c r="T14" t="s">
-        <v>19</v>
-      </c>
-      <c r="U14" t="s">
-        <v>45</v>
-      </c>
       <c r="V14" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="W14" t="s">
         <v>19</v>
@@ -3944,22 +3944,22 @@
         <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>37</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -3971,7 +3971,7 @@
         <v>19</v>
       </c>
       <c r="M15" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N15" t="s">
         <v>158</v>
@@ -3980,25 +3980,25 @@
         <v>150</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q15" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="R15" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s">
         <v>44</v>
       </c>
-      <c r="S15" t="s">
-        <v>19</v>
-      </c>
-      <c r="T15" t="s">
-        <v>19</v>
-      </c>
-      <c r="U15" t="s">
-        <v>45</v>
-      </c>
       <c r="V15" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="W15" t="s">
         <v>19</v>
@@ -4018,16 +4018,16 @@
         <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s">
         <v>37</v>
@@ -4045,7 +4045,7 @@
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N16" t="s">
         <v>160</v>
@@ -4054,22 +4054,22 @@
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q16" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="R16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S16" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s">
         <v>44</v>
-      </c>
-      <c r="S16" t="s">
-        <v>19</v>
-      </c>
-      <c r="T16" t="s">
-        <v>19</v>
-      </c>
-      <c r="U16" t="s">
-        <v>45</v>
       </c>
       <c r="V16" t="s">
         <v>19</v>
@@ -4098,10 +4098,10 @@
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
         <v>37</v>
@@ -4119,7 +4119,7 @@
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N17" t="s">
         <v>138</v>
@@ -4128,22 +4128,22 @@
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q17" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="R17" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s">
         <v>44</v>
-      </c>
-      <c r="S17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U17" t="s">
-        <v>45</v>
       </c>
       <c r="V17" t="s">
         <v>19</v>
@@ -4172,10 +4172,10 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
         <v>37</v>
@@ -4193,7 +4193,7 @@
         <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N18" t="s">
         <v>138</v>
@@ -4202,22 +4202,22 @@
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="Q18" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="R18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
         <v>44</v>
-      </c>
-      <c r="S18" t="s">
-        <v>19</v>
-      </c>
-      <c r="T18" t="s">
-        <v>19</v>
-      </c>
-      <c r="U18" t="s">
-        <v>45</v>
       </c>
       <c r="V18" t="s">
         <v>19</v>
@@ -4246,16 +4246,16 @@
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
         <v>37</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4267,7 +4267,7 @@
         <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N19" t="s">
         <v>143</v>
@@ -4276,22 +4276,22 @@
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="Q19" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R19" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
         <v>44</v>
-      </c>
-      <c r="S19" t="s">
-        <v>19</v>
-      </c>
-      <c r="T19" t="s">
-        <v>19</v>
-      </c>
-      <c r="U19" t="s">
-        <v>45</v>
       </c>
       <c r="V19" t="s">
         <v>19</v>
@@ -4320,10 +4320,10 @@
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>37</v>
@@ -4341,7 +4341,7 @@
         <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N20" t="s">
         <v>147</v>
@@ -4350,22 +4350,22 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="Q20" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="R20" t="s">
+        <v>43</v>
+      </c>
+      <c r="S20" t="s">
+        <v>19</v>
+      </c>
+      <c r="T20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
         <v>44</v>
-      </c>
-      <c r="S20" t="s">
-        <v>19</v>
-      </c>
-      <c r="T20" t="s">
-        <v>19</v>
-      </c>
-      <c r="U20" t="s">
-        <v>45</v>
       </c>
       <c r="V20" t="s">
         <v>19</v>
@@ -4394,16 +4394,16 @@
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
         <v>37</v>
       </c>
       <c r="I21" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4415,7 +4415,7 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N21" t="s">
         <v>149</v>
@@ -4424,22 +4424,22 @@
         <v>65</v>
       </c>
       <c r="P21" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q21" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="R21" t="s">
+        <v>43</v>
+      </c>
+      <c r="S21" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s">
         <v>44</v>
-      </c>
-      <c r="S21" t="s">
-        <v>19</v>
-      </c>
-      <c r="T21" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" t="s">
-        <v>45</v>
       </c>
       <c r="V21" t="s">
         <v>19</v>
@@ -4468,10 +4468,10 @@
         <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
         <v>37</v>
@@ -4489,7 +4489,7 @@
         <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N22" t="s">
         <v>143</v>
@@ -4498,22 +4498,22 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q22" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="R22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
         <v>44</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
-      </c>
-      <c r="T22" t="s">
-        <v>19</v>
-      </c>
-      <c r="U22" t="s">
-        <v>45</v>
       </c>
       <c r="V22" t="s">
         <v>19</v>
@@ -4542,16 +4542,16 @@
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="H23" t="s">
         <v>37</v>
       </c>
       <c r="I23" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4563,7 +4563,7 @@
         <v>19</v>
       </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N23" t="s">
         <v>156</v>
@@ -4572,22 +4572,22 @@
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q23" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="R23" t="s">
+        <v>43</v>
+      </c>
+      <c r="S23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T23" t="s">
+        <v>19</v>
+      </c>
+      <c r="U23" t="s">
         <v>44</v>
-      </c>
-      <c r="S23" t="s">
-        <v>19</v>
-      </c>
-      <c r="T23" t="s">
-        <v>19</v>
-      </c>
-      <c r="U23" t="s">
-        <v>45</v>
       </c>
       <c r="V23" t="s">
         <v>19</v>
@@ -4616,16 +4616,16 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G24" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
         <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4637,7 +4637,7 @@
         <v>19</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="N24" t="s">
         <v>140</v>
@@ -4646,22 +4646,22 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="R24" t="s">
+        <v>43</v>
+      </c>
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" t="s">
         <v>44</v>
-      </c>
-      <c r="S24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T24" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" t="s">
-        <v>45</v>
       </c>
       <c r="V24" t="s">
         <v>19</v>
@@ -4684,16 +4684,16 @@
         <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
         <v>37</v>
@@ -4711,7 +4711,7 @@
         <v>19</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N25" t="s">
         <v>158</v>
@@ -4720,25 +4720,25 @@
         <v>150</v>
       </c>
       <c r="P25" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R25" t="s">
+        <v>43</v>
+      </c>
+      <c r="S25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T25" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" t="s">
         <v>44</v>
       </c>
-      <c r="S25" t="s">
-        <v>19</v>
-      </c>
-      <c r="T25" t="s">
-        <v>19</v>
-      </c>
-      <c r="U25" t="s">
-        <v>45</v>
-      </c>
       <c r="V25" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="W25" t="s">
         <v>19</v>
@@ -4758,22 +4758,22 @@
         <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
         <v>37</v>
       </c>
       <c r="I26" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -4785,7 +4785,7 @@
         <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N26" t="s">
         <v>158</v>
@@ -4794,13 +4794,13 @@
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="Q26" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="R26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S26" t="s">
         <v>19</v>
@@ -4809,10 +4809,10 @@
         <v>19</v>
       </c>
       <c r="U26" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="V26" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="W26" t="s">
         <v>19</v>
@@ -4853,10 +4853,10 @@
         <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -5151,7 +5151,7 @@
         <v>193</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
         <v>19</v>
@@ -5213,7 +5213,7 @@
         <v>193</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
         <v>19</v>
@@ -5336,7 +5336,7 @@
         <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -5396,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
         <v>207</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>209</v>
@@ -5476,7 +5476,7 @@
         <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>212</v>
@@ -5496,7 +5496,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>213</v>
@@ -5536,7 +5536,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
         <v>215</v>
@@ -5602,7 +5602,7 @@
         <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>1</v>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -697,7 +697,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:26:04</t>
+    <t>08:32:09</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -697,7 +697,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:32:09</t>
+    <t>21:03:16</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="240">
   <si>
     <t>Term</t>
   </si>
@@ -73,6 +73,15 @@
     <t>CrossListings</t>
   </si>
   <si>
+    <t>CoreTag</t>
+  </si>
+  <si>
+    <t>SpecialTopic</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
     <t>In-Person</t>
   </si>
   <si>
+    <t>UGRAD</t>
+  </si>
+  <si>
     <t>SU</t>
   </si>
   <si>
@@ -166,498 +178,498 @@
     <t>09:00:00 - 11:30:00</t>
   </si>
   <si>
+    <t>SU-2</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Musical Patterns I (second semester)</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-1</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>FA-1</t>
+  </si>
+  <si>
+    <t>Information Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>FA-2</t>
+  </si>
+  <si>
+    <t>Information Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-B</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS203-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS368-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-AMUS181-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-BHAV121-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
+  </si>
+  <si>
+    <t>Off Campus</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>Winter Intensive</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Full term</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>First half</t>
+  </si>
+  <si>
     <t>Second</t>
   </si>
   <si>
-    <t>SU-Second</t>
-  </si>
-  <si>
-    <t>Summer session II</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:20:00</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Musical Patterns I (second semester)</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>Musical Patterns II</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Algorithms and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Discrete Rhythm</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>Harmonic Structures</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>Multivoice Analysis</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Corpus Studies I</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Corpus Studies II</t>
-  </si>
-  <si>
-    <t>BHAV</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Introduction to Behavioral Dynamics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>First</t>
-  </si>
-  <si>
-    <t>SU-First</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>Behavior in Sport</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>DIGI</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Information Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>Network Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as BHAV 306</t>
-  </si>
-  <si>
-    <t>BHAV 306</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Adaptive Systems</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>Information Capstone</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>FA-First</t>
-  </si>
-  <si>
-    <t>Information Ethics</t>
-  </si>
-  <si>
-    <t>First half of the term</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>FA-Second</t>
-  </si>
-  <si>
-    <t>Information Visualization</t>
-  </si>
-  <si>
-    <t>Second half of the term</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-B</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS228-A</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS203-A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS368-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-A</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV212-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV312-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI225-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI371-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI378-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI306-A</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-AMUS181-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-BHAV121-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS119-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS235-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS375-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV219-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI318-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI325-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-BHAV112-A</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Intensive terms meet daily</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>WI, SU</t>
-  </si>
-  <si>
-    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
-  </si>
-  <si>
-    <t>allow</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
-    <t>Off Campus</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
-    <t>Winter Intensive</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>Summer</t>
-  </si>
-  <si>
-    <t>Part</t>
-  </si>
-  <si>
-    <t>Full term</t>
-  </si>
-  <si>
-    <t>First half</t>
-  </si>
-  <si>
     <t>Second half</t>
   </si>
   <si>
@@ -691,13 +703,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-04</t>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>21:03:16</t>
+    <t>13:27:37</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1105,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1124,9 +1136,11 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1181,1685 +1195,1964 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T4" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
         <v>25</v>
       </c>
-      <c r="P2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="R2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="K7" t="s">
         <v>26</v>
-      </c>
-      <c r="R3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>23</v>
       </c>
       <c r="L7">
         <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
+      </c>
+      <c r="R7" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L8">
         <v>150</v>
       </c>
       <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
         <v>42</v>
       </c>
-      <c r="N8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s">
-        <v>43</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
       <c r="J9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="H10" t="s">
         <v>43</v>
       </c>
-      <c r="P9" t="s">
+      <c r="I10" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
       <c r="J10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+      <c r="T10" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" t="s">
         <v>56</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R11" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" t="s">
+        <v>22</v>
+      </c>
+      <c r="T11" t="s">
+        <v>22</v>
+      </c>
+      <c r="U11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="O11" t="s">
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" t="s">
         <v>43</v>
       </c>
-      <c r="P11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>19</v>
-      </c>
-      <c r="R11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R12" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" t="s">
+        <v>22</v>
+      </c>
+      <c r="T12" t="s">
+        <v>22</v>
+      </c>
+      <c r="U12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" t="s">
         <v>44</v>
       </c>
-      <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S14" t="s">
+        <v>22</v>
+      </c>
+      <c r="T14" t="s">
+        <v>22</v>
+      </c>
+      <c r="U14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s">
         <v>70</v>
       </c>
-      <c r="H15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" t="s">
-        <v>67</v>
-      </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T15" t="s">
+        <v>22</v>
+      </c>
+      <c r="U15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s">
         <v>70</v>
       </c>
-      <c r="H16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" t="s">
-        <v>67</v>
-      </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S16" t="s">
+        <v>22</v>
+      </c>
+      <c r="T16" t="s">
+        <v>22</v>
+      </c>
+      <c r="U16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S17" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" t="s">
-        <v>76</v>
-      </c>
       <c r="I18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S18" t="s">
+        <v>22</v>
+      </c>
+      <c r="T18" t="s">
+        <v>22</v>
+      </c>
+      <c r="U18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>87</v>
+      </c>
+      <c r="N19" t="s">
+        <v>88</v>
+      </c>
+      <c r="O19" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" t="s">
+        <v>22</v>
+      </c>
+      <c r="U19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
         <v>84</v>
       </c>
-      <c r="N19" t="s">
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" t="s">
         <v>85</v>
       </c>
-      <c r="O19" t="s">
-        <v>43</v>
-      </c>
-      <c r="P19" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>19</v>
-      </c>
-      <c r="R19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>82</v>
-      </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L20">
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>87</v>
+      </c>
+      <c r="N20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20" t="s">
+        <v>22</v>
+      </c>
+      <c r="T20" t="s">
+        <v>22</v>
+      </c>
+      <c r="U20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
         <v>84</v>
       </c>
-      <c r="N20" t="s">
-        <v>85</v>
-      </c>
-      <c r="O20" t="s">
-        <v>43</v>
-      </c>
-      <c r="P20" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>19</v>
-      </c>
-      <c r="R20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>87</v>
+      </c>
+      <c r="N21" t="s">
+        <v>88</v>
+      </c>
+      <c r="O21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>91</v>
+      </c>
+      <c r="R21" t="s">
+        <v>22</v>
+      </c>
+      <c r="S21" t="s">
+        <v>22</v>
+      </c>
+      <c r="T21" t="s">
+        <v>22</v>
+      </c>
+      <c r="U21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
         <v>84</v>
       </c>
-      <c r="N21" t="s">
-        <v>85</v>
-      </c>
-      <c r="O21" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>89</v>
-      </c>
-      <c r="R21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L22">
         <v>150</v>
       </c>
       <c r="M22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S22" t="s">
+        <v>22</v>
+      </c>
+      <c r="T22" t="s">
+        <v>22</v>
+      </c>
+      <c r="U22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S23" t="s">
+        <v>22</v>
+      </c>
+      <c r="T23" t="s">
+        <v>22</v>
+      </c>
+      <c r="U23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S24" t="s">
+        <v>22</v>
+      </c>
+      <c r="T24" t="s">
+        <v>22</v>
+      </c>
+      <c r="U24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S25" t="s">
+        <v>22</v>
+      </c>
+      <c r="T25" t="s">
+        <v>22</v>
+      </c>
+      <c r="U25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N26" t="s">
+        <v>108</v>
+      </c>
+      <c r="O26" t="s">
+        <v>46</v>
+      </c>
+      <c r="P26" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>22</v>
+      </c>
+      <c r="R26" t="s">
+        <v>22</v>
+      </c>
+      <c r="S26" t="s">
+        <v>22</v>
+      </c>
+      <c r="T26" t="s">
+        <v>22</v>
+      </c>
+      <c r="U26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" t="s">
         <v>106</v>
       </c>
-      <c r="O26" t="s">
-        <v>43</v>
-      </c>
-      <c r="P26" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>19</v>
-      </c>
-      <c r="R26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" t="s">
-        <v>39</v>
-      </c>
-      <c r="H27" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" t="s">
-        <v>104</v>
-      </c>
       <c r="J27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L27">
         <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N27" t="s">
+        <v>108</v>
+      </c>
+      <c r="O27" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>112</v>
+      </c>
+      <c r="R27" t="s">
+        <v>113</v>
+      </c>
+      <c r="S27" t="s">
+        <v>22</v>
+      </c>
+      <c r="T27" t="s">
+        <v>22</v>
+      </c>
+      <c r="U27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" t="s">
         <v>106</v>
       </c>
-      <c r="O27" t="s">
-        <v>43</v>
-      </c>
-      <c r="P27" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>110</v>
-      </c>
-      <c r="R27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" t="s">
-        <v>108</v>
-      </c>
-      <c r="I28" t="s">
-        <v>104</v>
-      </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L28">
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N28" t="s">
+        <v>108</v>
+      </c>
+      <c r="O28" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I29" t="s">
         <v>106</v>
       </c>
-      <c r="O28" t="s">
-        <v>43</v>
-      </c>
-      <c r="P28" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>19</v>
-      </c>
-      <c r="R28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" t="s">
-        <v>98</v>
-      </c>
-      <c r="I29" t="s">
-        <v>104</v>
-      </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N29" t="s">
+        <v>108</v>
+      </c>
+      <c r="O29" t="s">
+        <v>46</v>
+      </c>
+      <c r="P29" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>22</v>
+      </c>
+      <c r="R29" t="s">
+        <v>22</v>
+      </c>
+      <c r="S29" t="s">
+        <v>22</v>
+      </c>
+      <c r="T29" t="s">
+        <v>22</v>
+      </c>
+      <c r="U29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>79</v>
+      </c>
+      <c r="I30" t="s">
         <v>106</v>
       </c>
-      <c r="O29" t="s">
-        <v>43</v>
-      </c>
-      <c r="P29" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>19</v>
-      </c>
-      <c r="R29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" t="s">
-        <v>70</v>
-      </c>
-      <c r="H30" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" t="s">
-        <v>104</v>
-      </c>
       <c r="J30" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N30" t="s">
+        <v>108</v>
+      </c>
+      <c r="O30" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R30" t="s">
+        <v>22</v>
+      </c>
+      <c r="S30" t="s">
+        <v>22</v>
+      </c>
+      <c r="T30" t="s">
+        <v>22</v>
+      </c>
+      <c r="U30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I31" t="s">
         <v>106</v>
       </c>
-      <c r="O30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P30" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>119</v>
-      </c>
-      <c r="R30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" t="s">
-        <v>76</v>
-      </c>
-      <c r="I31" t="s">
-        <v>104</v>
-      </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P31" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q31" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R31" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="S31" t="s">
+        <v>22</v>
+      </c>
+      <c r="T31" t="s">
+        <v>22</v>
+      </c>
+      <c r="U31" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2870,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2895,17 +3188,18 @@
     <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2929,22 +3223,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -2953,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -2965,39 +3259,45 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3006,72 +3306,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>139</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>137</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3080,72 +3386,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3154,72 +3466,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O4">
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3228,72 +3546,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="R5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3302,72 +3626,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3376,72 +3706,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="R7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3450,72 +3786,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q8" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" t="s">
+        <v>22</v>
+      </c>
+      <c r="W8" t="s">
+        <v>22</v>
+      </c>
+      <c r="X8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>84</v>
       </c>
-      <c r="R8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" t="s">
-        <v>19</v>
-      </c>
-      <c r="W8" t="s">
-        <v>19</v>
-      </c>
-      <c r="X8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>81</v>
-      </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3524,72 +3866,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3598,72 +3946,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3672,72 +4026,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -3746,72 +4106,78 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -3820,72 +4186,78 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="W13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -3894,72 +4266,78 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O14">
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -3968,72 +4346,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O15">
         <v>150</v>
       </c>
       <c r="P15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="s">
+        <v>65</v>
+      </c>
+      <c r="R15" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T15" t="s">
+        <v>22</v>
+      </c>
+      <c r="U15" t="s">
+        <v>47</v>
+      </c>
+      <c r="V15" t="s">
+        <v>67</v>
+      </c>
+      <c r="W15" t="s">
+        <v>22</v>
+      </c>
+      <c r="X15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="R15" t="s">
-        <v>43</v>
-      </c>
-      <c r="S15" t="s">
-        <v>19</v>
-      </c>
-      <c r="T15" t="s">
-        <v>19</v>
-      </c>
-      <c r="U15" t="s">
-        <v>44</v>
-      </c>
-      <c r="V15" t="s">
-        <v>64</v>
-      </c>
-      <c r="W15" t="s">
-        <v>19</v>
-      </c>
-      <c r="X15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" t="s">
-        <v>59</v>
-      </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4042,72 +4426,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O16">
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
         <v>27</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" t="s">
-        <v>24</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4116,72 +4506,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4190,72 +4586,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4264,72 +4666,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4338,72 +4746,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4412,72 +4826,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O21">
         <v>65</v>
       </c>
       <c r="P21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q21" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" t="s">
+        <v>22</v>
+      </c>
+      <c r="T21" t="s">
+        <v>22</v>
+      </c>
+      <c r="U21" t="s">
+        <v>47</v>
+      </c>
+      <c r="V21" t="s">
+        <v>22</v>
+      </c>
+      <c r="W21" t="s">
+        <v>22</v>
+      </c>
+      <c r="X21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
         <v>84</v>
       </c>
-      <c r="R21" t="s">
-        <v>43</v>
-      </c>
-      <c r="S21" t="s">
-        <v>19</v>
-      </c>
-      <c r="T21" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" t="s">
-        <v>44</v>
-      </c>
-      <c r="V21" t="s">
-        <v>19</v>
-      </c>
-      <c r="W21" t="s">
-        <v>19</v>
-      </c>
-      <c r="X21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" t="s">
-        <v>81</v>
-      </c>
       <c r="G22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4486,72 +4906,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4560,72 +4986,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4634,72 +5066,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -4708,72 +5146,78 @@
         <v>2</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O25">
         <v>150</v>
       </c>
       <c r="P25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -4782,43 +5226,49 @@
         <v>2</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O26">
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="W26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X26" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4839,7 +5289,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4850,13 +5300,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4878,19 +5328,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -4898,62 +5348,62 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4988,61 +5438,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -5050,188 +5500,188 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K3" t="s">
+        <v>198</v>
+      </c>
+      <c r="L3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" t="s">
         <v>195</v>
       </c>
-      <c r="K3" t="s">
-        <v>196</v>
-      </c>
-      <c r="L3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M3" t="s">
-        <v>193</v>
-      </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" t="s">
         <v>195</v>
       </c>
-      <c r="K4" t="s">
-        <v>196</v>
-      </c>
-      <c r="L4" t="s">
-        <v>160</v>
-      </c>
-      <c r="M4" t="s">
-        <v>193</v>
-      </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -5253,122 +5703,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5376,19 +5826,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,19 +5846,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5416,19 +5866,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5436,33 +5886,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5473,16 +5923,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5493,16 +5943,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -5513,16 +5963,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5533,16 +5983,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -5553,16 +6003,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -5573,16 +6023,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -5593,16 +6043,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5628,90 +6078,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="244">
   <si>
     <t>Term</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Colocations</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -595,6 +598,15 @@
     <t>Meets</t>
   </si>
   <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>Intensive terms meet daily</t>
   </si>
   <si>
@@ -607,6 +619,9 @@
     <t>WI, SU</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
   </si>
   <si>
@@ -703,13 +718,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-06</t>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>13:27:37</t>
+    <t>08:51:36</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -725,9 +740,6 @@
   </si>
   <si>
     <t>Time Stamp In File Name</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>Default Department</t>
@@ -1117,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1138,9 +1150,10 @@
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1204,1955 +1217,2048 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="K7" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T4" t="s">
-        <v>22</v>
-      </c>
-      <c r="U4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" t="s">
-        <v>22</v>
-      </c>
-      <c r="S5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" t="s">
-        <v>22</v>
-      </c>
-      <c r="S6" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6" t="s">
-        <v>22</v>
-      </c>
-      <c r="U6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
       </c>
       <c r="L7">
         <v>65</v>
       </c>
       <c r="M7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
         <v>45</v>
       </c>
-      <c r="N7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>22</v>
-      </c>
-      <c r="R7" t="s">
-        <v>22</v>
-      </c>
-      <c r="S7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T7" t="s">
-        <v>22</v>
-      </c>
-      <c r="U7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="J8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8">
         <v>150</v>
       </c>
       <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
         <v>45</v>
       </c>
-      <c r="N8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" t="s">
-        <v>22</v>
-      </c>
-      <c r="S8" t="s">
-        <v>22</v>
-      </c>
-      <c r="T8" t="s">
-        <v>22</v>
-      </c>
-      <c r="U8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
-      </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
         <v>45</v>
       </c>
-      <c r="N9" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" t="s">
-        <v>22</v>
-      </c>
-      <c r="S9" t="s">
-        <v>22</v>
-      </c>
-      <c r="T9" t="s">
-        <v>22</v>
-      </c>
-      <c r="U9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
-      </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>49</v>
+      </c>
+      <c r="V10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
         <v>27</v>
-      </c>
-      <c r="O10" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" t="s">
-        <v>22</v>
-      </c>
-      <c r="S10" t="s">
-        <v>22</v>
-      </c>
-      <c r="T10" t="s">
-        <v>22</v>
-      </c>
-      <c r="U10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
         <v>61</v>
       </c>
-      <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R11" t="s">
-        <v>22</v>
-      </c>
-      <c r="S11" t="s">
-        <v>22</v>
-      </c>
-      <c r="T11" t="s">
-        <v>22</v>
-      </c>
-      <c r="U11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" t="s">
-        <v>60</v>
-      </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" t="s">
+        <v>23</v>
+      </c>
+      <c r="U13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="S13" t="s">
-        <v>22</v>
-      </c>
-      <c r="T13" t="s">
-        <v>22</v>
-      </c>
-      <c r="U13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
+        <v>72</v>
+      </c>
+      <c r="N14" t="s">
+        <v>67</v>
+      </c>
+      <c r="O14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T14" t="s">
+        <v>23</v>
+      </c>
+      <c r="U14" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" t="s">
         <v>71</v>
       </c>
-      <c r="N14" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>22</v>
-      </c>
-      <c r="R14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T14" t="s">
-        <v>22</v>
-      </c>
-      <c r="U14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s">
-        <v>70</v>
-      </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O15" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" t="s">
+        <v>23</v>
+      </c>
+      <c r="U15" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
         <v>75</v>
       </c>
-      <c r="N15" t="s">
-        <v>66</v>
-      </c>
-      <c r="O15" t="s">
-        <v>46</v>
-      </c>
-      <c r="P15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>22</v>
-      </c>
-      <c r="R15" t="s">
-        <v>22</v>
-      </c>
-      <c r="S15" t="s">
-        <v>22</v>
-      </c>
-      <c r="T15" t="s">
-        <v>22</v>
-      </c>
-      <c r="U15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" t="s">
-        <v>74</v>
-      </c>
       <c r="I16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" t="s">
+        <v>23</v>
+      </c>
+      <c r="U16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="R16" t="s">
-        <v>22</v>
-      </c>
-      <c r="S16" t="s">
-        <v>22</v>
-      </c>
-      <c r="T16" t="s">
-        <v>22</v>
-      </c>
-      <c r="U16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17" t="s">
+        <v>82</v>
+      </c>
+      <c r="N17" t="s">
+        <v>67</v>
+      </c>
+      <c r="O17" t="s">
+        <v>47</v>
+      </c>
+      <c r="P17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>23</v>
+      </c>
+      <c r="R17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" t="s">
+        <v>23</v>
+      </c>
+      <c r="T17" t="s">
+        <v>23</v>
+      </c>
+      <c r="U17" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
         <v>81</v>
       </c>
-      <c r="N17" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" t="s">
-        <v>46</v>
-      </c>
-      <c r="P17" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>22</v>
-      </c>
-      <c r="R17" t="s">
-        <v>22</v>
-      </c>
-      <c r="S17" t="s">
-        <v>22</v>
-      </c>
-      <c r="T17" t="s">
-        <v>22</v>
-      </c>
-      <c r="U17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" t="s">
-        <v>80</v>
-      </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q18" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" t="s">
+        <v>23</v>
+      </c>
+      <c r="U18" t="s">
+        <v>49</v>
+      </c>
+      <c r="V18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="R18" t="s">
-        <v>22</v>
-      </c>
-      <c r="S18" t="s">
-        <v>22</v>
-      </c>
-      <c r="T18" t="s">
-        <v>22</v>
-      </c>
-      <c r="U18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" t="s">
+        <v>89</v>
+      </c>
+      <c r="O19" t="s">
+        <v>47</v>
+      </c>
+      <c r="P19" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" t="s">
+        <v>23</v>
+      </c>
+      <c r="T19" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" t="s">
         <v>87</v>
       </c>
-      <c r="N19" t="s">
-        <v>88</v>
-      </c>
-      <c r="O19" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>22</v>
-      </c>
-      <c r="R19" t="s">
-        <v>22</v>
-      </c>
-      <c r="S19" t="s">
-        <v>22</v>
-      </c>
-      <c r="T19" t="s">
-        <v>22</v>
-      </c>
-      <c r="U19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" t="s">
-        <v>86</v>
-      </c>
       <c r="J20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L20">
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" t="s">
+        <v>47</v>
+      </c>
+      <c r="P20" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" t="s">
+        <v>23</v>
+      </c>
+      <c r="S20" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" t="s">
+        <v>23</v>
+      </c>
+      <c r="U20" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" t="s">
         <v>87</v>
       </c>
-      <c r="N20" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>22</v>
-      </c>
-      <c r="R20" t="s">
-        <v>22</v>
-      </c>
-      <c r="S20" t="s">
-        <v>22</v>
-      </c>
-      <c r="T20" t="s">
-        <v>22</v>
-      </c>
-      <c r="U20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" t="s">
-        <v>86</v>
-      </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" t="s">
+        <v>89</v>
+      </c>
+      <c r="O21" t="s">
+        <v>47</v>
+      </c>
+      <c r="P21" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>92</v>
+      </c>
+      <c r="R21" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" t="s">
         <v>87</v>
       </c>
-      <c r="N21" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>91</v>
-      </c>
-      <c r="R21" t="s">
-        <v>22</v>
-      </c>
-      <c r="S21" t="s">
-        <v>22</v>
-      </c>
-      <c r="T21" t="s">
-        <v>22</v>
-      </c>
-      <c r="U21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" t="s">
-        <v>86</v>
-      </c>
       <c r="J22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L22">
         <v>150</v>
       </c>
       <c r="M22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q22" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" t="s">
+        <v>23</v>
+      </c>
+      <c r="T22" t="s">
+        <v>23</v>
+      </c>
+      <c r="U22" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="R22" t="s">
-        <v>22</v>
-      </c>
-      <c r="S22" t="s">
-        <v>22</v>
-      </c>
-      <c r="T22" t="s">
-        <v>22</v>
-      </c>
-      <c r="U22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q24" t="s">
+        <v>23</v>
+      </c>
+      <c r="R24" t="s">
+        <v>23</v>
+      </c>
+      <c r="S24" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" t="s">
+        <v>23</v>
+      </c>
+      <c r="U24" t="s">
+        <v>49</v>
+      </c>
+      <c r="V24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="R24" t="s">
-        <v>22</v>
-      </c>
-      <c r="S24" t="s">
-        <v>22</v>
-      </c>
-      <c r="T24" t="s">
-        <v>22</v>
-      </c>
-      <c r="U24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q25" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" t="s">
+        <v>23</v>
+      </c>
+      <c r="S25" t="s">
+        <v>23</v>
+      </c>
+      <c r="T25" t="s">
+        <v>23</v>
+      </c>
+      <c r="U25" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
-      <c r="R25" t="s">
-        <v>22</v>
-      </c>
-      <c r="S25" t="s">
-        <v>22</v>
-      </c>
-      <c r="T25" t="s">
-        <v>22</v>
-      </c>
-      <c r="U25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N26" t="s">
+        <v>109</v>
+      </c>
+      <c r="O26" t="s">
+        <v>47</v>
+      </c>
+      <c r="P26" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" t="s">
+        <v>23</v>
+      </c>
+      <c r="T26" t="s">
+        <v>23</v>
+      </c>
+      <c r="U26" t="s">
+        <v>49</v>
+      </c>
+      <c r="V26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" t="s">
         <v>107</v>
       </c>
-      <c r="N26" t="s">
-        <v>108</v>
-      </c>
-      <c r="O26" t="s">
-        <v>46</v>
-      </c>
-      <c r="P26" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>22</v>
-      </c>
-      <c r="R26" t="s">
-        <v>22</v>
-      </c>
-      <c r="S26" t="s">
-        <v>22</v>
-      </c>
-      <c r="T26" t="s">
-        <v>22</v>
-      </c>
-      <c r="U26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" t="s">
-        <v>110</v>
-      </c>
-      <c r="I27" t="s">
-        <v>106</v>
-      </c>
       <c r="J27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L27">
         <v>65</v>
       </c>
       <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N27" t="s">
+        <v>109</v>
+      </c>
+      <c r="O27" t="s">
+        <v>47</v>
+      </c>
+      <c r="P27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>113</v>
+      </c>
+      <c r="R27" t="s">
+        <v>114</v>
+      </c>
+      <c r="S27" t="s">
+        <v>23</v>
+      </c>
+      <c r="T27" t="s">
+        <v>23</v>
+      </c>
+      <c r="U27" t="s">
+        <v>49</v>
+      </c>
+      <c r="V27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" t="s">
         <v>111</v>
       </c>
-      <c r="N27" t="s">
-        <v>108</v>
-      </c>
-      <c r="O27" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>112</v>
-      </c>
-      <c r="R27" t="s">
-        <v>113</v>
-      </c>
-      <c r="S27" t="s">
-        <v>22</v>
-      </c>
-      <c r="T27" t="s">
-        <v>22</v>
-      </c>
-      <c r="U27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" t="s">
-        <v>110</v>
-      </c>
       <c r="I28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L28">
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q29" t="s">
+        <v>23</v>
+      </c>
+      <c r="R29" t="s">
+        <v>23</v>
+      </c>
+      <c r="S29" t="s">
+        <v>23</v>
+      </c>
+      <c r="T29" t="s">
+        <v>23</v>
+      </c>
+      <c r="U29" t="s">
+        <v>49</v>
+      </c>
+      <c r="V29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>22</v>
       </c>
-      <c r="R29" t="s">
-        <v>22</v>
-      </c>
-      <c r="S29" t="s">
-        <v>22</v>
-      </c>
-      <c r="T29" t="s">
-        <v>22</v>
-      </c>
-      <c r="U29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>21</v>
-      </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R30" t="s">
+        <v>23</v>
+      </c>
+      <c r="S30" t="s">
+        <v>23</v>
+      </c>
+      <c r="T30" t="s">
+        <v>23</v>
+      </c>
+      <c r="U30" t="s">
+        <v>49</v>
+      </c>
+      <c r="V30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="S30" t="s">
-        <v>22</v>
-      </c>
-      <c r="T30" t="s">
-        <v>22</v>
-      </c>
-      <c r="U30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U31" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="V31" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3193,13 +3299,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3223,22 +3329,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3247,10 +3353,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3259,10 +3365,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3273,31 +3379,31 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3306,78 +3412,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3386,78 +3492,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3466,78 +3572,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O4">
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3546,78 +3652,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3626,78 +3732,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3706,78 +3812,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3786,78 +3892,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3866,78 +3972,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3946,78 +4052,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -4026,78 +4132,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -4106,78 +4212,78 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="W12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -4186,78 +4292,78 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
         <v>109</v>
-      </c>
-      <c r="H14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" t="s">
-        <v>108</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -4266,78 +4372,78 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O14">
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4346,78 +4452,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O15">
         <v>150</v>
       </c>
       <c r="P15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4426,78 +4532,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O16">
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4506,78 +4612,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4586,78 +4692,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4666,78 +4772,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4746,78 +4852,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4826,78 +4932,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O21">
         <v>65</v>
       </c>
       <c r="P21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4906,78 +5012,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4986,78 +5092,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -5066,78 +5172,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -5146,78 +5252,78 @@
         <v>2</v>
       </c>
       <c r="L25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O25">
         <v>150</v>
       </c>
       <c r="P25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -5226,49 +5332,49 @@
         <v>2</v>
       </c>
       <c r="L26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O26">
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5289,7 +5395,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5300,13 +5406,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5328,19 +5434,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5348,62 +5454,62 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5414,7 +5520,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5433,255 +5539,293 @@
     <col min="17" max="17" width="4" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
+        <v>200</v>
+      </c>
+      <c r="W2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>192</v>
-      </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>200</v>
+      </c>
+      <c r="W3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" t="s">
         <v>197</v>
       </c>
-      <c r="K3" t="s">
-        <v>198</v>
-      </c>
-      <c r="L3" t="s">
-        <v>160</v>
-      </c>
-      <c r="M3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>193</v>
-      </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>200</v>
+      </c>
+      <c r="W4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5703,122 +5847,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5826,19 +5970,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5846,19 +5990,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5866,19 +6010,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5886,33 +6030,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5923,16 +6067,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5943,16 +6087,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -5963,16 +6107,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5983,16 +6127,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -6003,16 +6147,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C16" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -6023,16 +6167,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -6043,16 +6187,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6078,90 +6222,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -208,459 +208,459 @@
     <t>Musical Patterns II</t>
   </si>
   <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>SP-0</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-1</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>FA-1</t>
+  </si>
+  <si>
+    <t>Information Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>FA-2</t>
+  </si>
+  <si>
+    <t>Information Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-B</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS203-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS368-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-AMUS181-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-BHAV121-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
+  </si>
+  <si>
+    <t>Off Campus</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
     <t>WI</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Algorithms and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Discrete Rhythm</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>Harmonic Structures</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>Multivoice Analysis</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Corpus Studies I</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Corpus Studies II</t>
-  </si>
-  <si>
-    <t>BHAV</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Introduction to Behavioral Dynamics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>SU-1</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>Behavior in Sport</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>DIGI</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Information Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>Network Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as BHAV 306</t>
-  </si>
-  <si>
-    <t>BHAV 306</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Adaptive Systems</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>Information Capstone</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>FA-1</t>
-  </si>
-  <si>
-    <t>Information Ethics</t>
-  </si>
-  <si>
-    <t>First half of the term</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>FA-2</t>
-  </si>
-  <si>
-    <t>Information Visualization</t>
-  </si>
-  <si>
-    <t>Second half of the term</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-B</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS228-A</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS203-A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS368-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-A</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV212-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV312-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI225-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI371-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI378-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI306-A</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-AMUS181-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-BHAV121-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS119-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS235-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS375-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV219-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI318-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI325-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-BHAV112-A</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Intensive terms meet daily</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>WI, SU</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
-  </si>
-  <si>
-    <t>allow</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
-    <t>Off Campus</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
     <t>Winter Intensive</t>
   </si>
   <si>
@@ -724,7 +724,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:43</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -1998,19 +1998,19 @@
         <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" t="s">
         <v>66</v>
-      </c>
-      <c r="N13" t="s">
-        <v>67</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
@@ -2019,7 +2019,7 @@
         <v>48</v>
       </c>
       <c r="Q13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R13" t="s">
         <v>23</v>
@@ -2045,7 +2045,7 @@
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2060,10 +2060,10 @@
         <v>43</v>
       </c>
       <c r="H14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" t="s">
         <v>70</v>
-      </c>
-      <c r="I14" t="s">
-        <v>71</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
@@ -2075,10 +2075,10 @@
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
@@ -2113,7 +2113,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>41</v>
@@ -2125,13 +2125,13 @@
         <v>42</v>
       </c>
       <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
         <v>74</v>
       </c>
-      <c r="H15" t="s">
-        <v>75</v>
-      </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
@@ -2143,10 +2143,10 @@
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
@@ -2181,7 +2181,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -2193,13 +2193,13 @@
         <v>42</v>
       </c>
       <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
         <v>74</v>
       </c>
-      <c r="H16" t="s">
-        <v>75</v>
-      </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J16" t="s">
         <v>26</v>
@@ -2211,10 +2211,10 @@
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
@@ -2249,7 +2249,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>41</v>
@@ -2261,13 +2261,13 @@
         <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" t="s">
         <v>80</v>
-      </c>
-      <c r="I17" t="s">
-        <v>81</v>
       </c>
       <c r="J17" t="s">
         <v>26</v>
@@ -2279,10 +2279,10 @@
         <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O17" t="s">
         <v>47</v>
@@ -2317,7 +2317,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>41</v>
@@ -2329,13 +2329,13 @@
         <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" t="s">
         <v>80</v>
-      </c>
-      <c r="I18" t="s">
-        <v>81</v>
       </c>
       <c r="J18" t="s">
         <v>26</v>
@@ -2347,7 +2347,7 @@
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
         <v>34</v>
@@ -2382,7 +2382,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
@@ -2400,10 +2400,10 @@
         <v>43</v>
       </c>
       <c r="H19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" t="s">
         <v>86</v>
-      </c>
-      <c r="I19" t="s">
-        <v>87</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -2415,10 +2415,10 @@
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>87</v>
+      </c>
+      <c r="N19" t="s">
         <v>88</v>
-      </c>
-      <c r="N19" t="s">
-        <v>89</v>
       </c>
       <c r="O19" t="s">
         <v>47</v>
@@ -2450,7 +2450,7 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
@@ -2468,10 +2468,10 @@
         <v>43</v>
       </c>
       <c r="H20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" t="s">
         <v>86</v>
-      </c>
-      <c r="I20" t="s">
-        <v>87</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2483,10 +2483,10 @@
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>87</v>
+      </c>
+      <c r="N20" t="s">
         <v>88</v>
-      </c>
-      <c r="N20" t="s">
-        <v>89</v>
       </c>
       <c r="O20" t="s">
         <v>47</v>
@@ -2518,7 +2518,7 @@
         <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
@@ -2539,31 +2539,31 @@
         <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
         <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>87</v>
+      </c>
+      <c r="N21" t="s">
         <v>88</v>
-      </c>
-      <c r="N21" t="s">
-        <v>89</v>
       </c>
       <c r="O21" t="s">
         <v>47</v>
       </c>
       <c r="P21" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q21" t="s">
         <v>91</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>92</v>
       </c>
       <c r="R21" t="s">
         <v>23</v>
@@ -2583,13 +2583,13 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>41</v>
@@ -2604,22 +2604,22 @@
         <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L22">
         <v>150</v>
       </c>
       <c r="M22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N22" t="s">
         <v>37</v>
@@ -2654,10 +2654,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
@@ -2669,13 +2669,13 @@
         <v>42</v>
       </c>
       <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
         <v>74</v>
       </c>
-      <c r="H23" t="s">
-        <v>75</v>
-      </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
         <v>26</v>
@@ -2687,7 +2687,7 @@
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
         <v>37</v>
@@ -2722,10 +2722,10 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
@@ -2737,13 +2737,13 @@
         <v>42</v>
       </c>
       <c r="G24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" t="s">
         <v>74</v>
       </c>
-      <c r="H24" t="s">
-        <v>75</v>
-      </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
         <v>26</v>
@@ -2755,7 +2755,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N24" t="s">
         <v>37</v>
@@ -2790,10 +2790,10 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
@@ -2805,13 +2805,13 @@
         <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
         <v>26</v>
@@ -2823,10 +2823,10 @@
         <v>100</v>
       </c>
       <c r="M25" t="s">
+        <v>101</v>
+      </c>
+      <c r="N25" t="s">
         <v>102</v>
-      </c>
-      <c r="N25" t="s">
-        <v>103</v>
       </c>
       <c r="O25" t="s">
         <v>47</v>
@@ -2858,10 +2858,10 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
         <v>104</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>41</v>
@@ -2873,13 +2873,13 @@
         <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" t="s">
         <v>106</v>
-      </c>
-      <c r="I26" t="s">
-        <v>107</v>
       </c>
       <c r="J26" t="s">
         <v>26</v>
@@ -2891,10 +2891,10 @@
         <v>100</v>
       </c>
       <c r="M26" t="s">
+        <v>107</v>
+      </c>
+      <c r="N26" t="s">
         <v>108</v>
-      </c>
-      <c r="N26" t="s">
-        <v>109</v>
       </c>
       <c r="O26" t="s">
         <v>47</v>
@@ -2926,10 +2926,10 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>41</v>
@@ -2944,10 +2944,10 @@
         <v>43</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J27" t="s">
         <v>26</v>
@@ -2959,10 +2959,10 @@
         <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" t="s">
         <v>47</v>
@@ -2971,10 +2971,10 @@
         <v>48</v>
       </c>
       <c r="Q27" t="s">
+        <v>112</v>
+      </c>
+      <c r="R27" t="s">
         <v>113</v>
-      </c>
-      <c r="R27" t="s">
-        <v>114</v>
       </c>
       <c r="S27" t="s">
         <v>23</v>
@@ -2994,10 +2994,10 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -3012,10 +3012,10 @@
         <v>43</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J28" t="s">
         <v>26</v>
@@ -3027,10 +3027,10 @@
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O28" t="s">
         <v>47</v>
@@ -3062,10 +3062,10 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>
@@ -3077,13 +3077,13 @@
         <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J29" t="s">
         <v>26</v>
@@ -3095,10 +3095,10 @@
         <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O29" t="s">
         <v>47</v>
@@ -3130,10 +3130,10 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
@@ -3145,28 +3145,28 @@
         <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J30" t="s">
         <v>33</v>
       </c>
       <c r="K30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O30" t="s">
         <v>47</v>
@@ -3175,7 +3175,7 @@
         <v>48</v>
       </c>
       <c r="Q30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R30" t="s">
         <v>23</v>
@@ -3198,10 +3198,10 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>41</v>
@@ -3213,28 +3213,28 @@
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J31" t="s">
         <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
         <v>47</v>
@@ -3243,7 +3243,7 @@
         <v>48</v>
       </c>
       <c r="Q31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R31" t="s">
         <v>23</v>
@@ -3299,13 +3299,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3329,22 +3329,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3353,10 +3353,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3365,10 +3365,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3379,13 +3379,13 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>139</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>140</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -3418,7 +3418,7 @@
         <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O2">
         <v>65</v>
@@ -3459,13 +3459,13 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3498,7 +3498,7 @@
         <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O3">
         <v>65</v>
@@ -3539,13 +3539,13 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -3578,7 +3578,7 @@
         <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O4">
         <v>65</v>
@@ -3619,13 +3619,13 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -3637,13 +3637,13 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
         <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3655,19 +3655,19 @@
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R5" t="s">
         <v>47</v>
@@ -3699,13 +3699,13 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -3717,13 +3717,13 @@
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
         <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3738,16 +3738,16 @@
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q6" t="s">
         <v>71</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>72</v>
       </c>
       <c r="R6" t="s">
         <v>47</v>
@@ -3779,13 +3779,13 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -3797,13 +3797,13 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
         <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3815,19 +3815,19 @@
         <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="s">
         <v>81</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>82</v>
       </c>
       <c r="R7" t="s">
         <v>47</v>
@@ -3859,13 +3859,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -3874,7 +3874,7 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
         <v>40</v>
@@ -3883,7 +3883,7 @@
         <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3898,16 +3898,16 @@
         <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="s">
         <v>87</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>88</v>
       </c>
       <c r="R8" t="s">
         <v>47</v>
@@ -3939,13 +3939,13 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -3954,10 +3954,10 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H9" t="s">
         <v>41</v>
@@ -3975,19 +3975,19 @@
         <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R9" t="s">
         <v>47</v>
@@ -4019,13 +4019,13 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -4034,16 +4034,16 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
         <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -4055,19 +4055,19 @@
         <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R10" t="s">
         <v>47</v>
@@ -4099,13 +4099,13 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -4114,16 +4114,16 @@
         <v>26</v>
       </c>
       <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
         <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -4135,19 +4135,19 @@
         <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q11" t="s">
         <v>107</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>108</v>
       </c>
       <c r="R11" t="s">
         <v>47</v>
@@ -4179,13 +4179,13 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -4194,16 +4194,16 @@
         <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H12" t="s">
         <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -4215,19 +4215,19 @@
         <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R12" t="s">
         <v>47</v>
@@ -4242,7 +4242,7 @@
         <v>48</v>
       </c>
       <c r="V12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W12" t="s">
         <v>23</v>
@@ -4259,13 +4259,13 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -4274,16 +4274,16 @@
         <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
         <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -4295,19 +4295,19 @@
         <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R13" t="s">
         <v>47</v>
@@ -4322,7 +4322,7 @@
         <v>48</v>
       </c>
       <c r="V13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W13" t="s">
         <v>23</v>
@@ -4339,13 +4339,13 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -4354,16 +4354,16 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -4378,16 +4378,16 @@
         <v>43</v>
       </c>
       <c r="N14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O14">
         <v>65</v>
       </c>
       <c r="P14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R14" t="s">
         <v>47</v>
@@ -4402,7 +4402,7 @@
         <v>48</v>
       </c>
       <c r="V14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="W14" t="s">
         <v>23</v>
@@ -4419,31 +4419,31 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4458,7 +4458,7 @@
         <v>52</v>
       </c>
       <c r="N15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O15">
         <v>150</v>
@@ -4467,7 +4467,7 @@
         <v>45</v>
       </c>
       <c r="Q15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R15" t="s">
         <v>47</v>
@@ -4482,7 +4482,7 @@
         <v>48</v>
       </c>
       <c r="V15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W15" t="s">
         <v>23</v>
@@ -4499,25 +4499,25 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
         <v>41</v>
@@ -4538,16 +4538,16 @@
         <v>52</v>
       </c>
       <c r="N16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O16">
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R16" t="s">
         <v>47</v>
@@ -4579,13 +4579,13 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -4618,7 +4618,7 @@
         <v>43</v>
       </c>
       <c r="N17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O17">
         <v>65</v>
@@ -4659,13 +4659,13 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -4698,7 +4698,7 @@
         <v>43</v>
       </c>
       <c r="N18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O18">
         <v>65</v>
@@ -4739,13 +4739,13 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -4757,13 +4757,13 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
         <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4775,19 +4775,19 @@
         <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R19" t="s">
         <v>47</v>
@@ -4819,13 +4819,13 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -4837,7 +4837,7 @@
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>41</v>
@@ -4855,19 +4855,19 @@
         <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R20" t="s">
         <v>47</v>
@@ -4899,13 +4899,13 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
         <v>31</v>
@@ -4914,7 +4914,7 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
         <v>40</v>
@@ -4923,7 +4923,7 @@
         <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4938,16 +4938,16 @@
         <v>43</v>
       </c>
       <c r="N21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O21">
         <v>65</v>
       </c>
       <c r="P21" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q21" t="s">
         <v>87</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>88</v>
       </c>
       <c r="R21" t="s">
         <v>47</v>
@@ -4979,13 +4979,13 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
@@ -4994,10 +4994,10 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H22" t="s">
         <v>41</v>
@@ -5015,19 +5015,19 @@
         <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R22" t="s">
         <v>47</v>
@@ -5059,13 +5059,13 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
         <v>31</v>
@@ -5074,16 +5074,16 @@
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H23" t="s">
         <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -5098,16 +5098,16 @@
         <v>43</v>
       </c>
       <c r="N23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R23" t="s">
         <v>47</v>
@@ -5139,13 +5139,13 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>31</v>
@@ -5154,16 +5154,16 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H24" t="s">
         <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -5175,19 +5175,19 @@
         <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R24" t="s">
         <v>47</v>
@@ -5219,13 +5219,13 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
         <v>50</v>
@@ -5258,7 +5258,7 @@
         <v>52</v>
       </c>
       <c r="N25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O25">
         <v>150</v>
@@ -5299,13 +5299,13 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
         <v>50</v>
@@ -5314,7 +5314,7 @@
         <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
         <v>40</v>
@@ -5323,7 +5323,7 @@
         <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -5338,16 +5338,16 @@
         <v>52</v>
       </c>
       <c r="N26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O26">
         <v>150</v>
       </c>
       <c r="P26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q26" t="s">
         <v>87</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>88</v>
       </c>
       <c r="R26" t="s">
         <v>47</v>
@@ -5359,10 +5359,10 @@
         <v>23</v>
       </c>
       <c r="U26" t="s">
+        <v>90</v>
+      </c>
+      <c r="V26" t="s">
         <v>91</v>
-      </c>
-      <c r="V26" t="s">
-        <v>92</v>
       </c>
       <c r="W26" t="s">
         <v>23</v>
@@ -5395,7 +5395,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5406,13 +5406,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5434,19 +5434,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
@@ -5503,7 +5503,7 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5546,70 +5546,70 @@
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -5617,82 +5617,82 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
         <v>196</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>197</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>198</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
         <v>199</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>200</v>
-      </c>
-      <c r="W2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" t="s">
         <v>196</v>
       </c>
-      <c r="B3" t="s">
-        <v>197</v>
-      </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
@@ -5715,16 +5715,16 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" t="s">
         <v>202</v>
       </c>
-      <c r="K3" t="s">
-        <v>203</v>
-      </c>
       <c r="L3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N3" t="s">
         <v>52</v>
@@ -5751,7 +5751,7 @@
         <v>23</v>
       </c>
       <c r="V3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W3" t="s">
         <v>23</v>
@@ -5759,11 +5759,11 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" t="s">
         <v>196</v>
       </c>
-      <c r="B4" t="s">
-        <v>197</v>
-      </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
@@ -5786,16 +5786,16 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" t="s">
         <v>202</v>
       </c>
-      <c r="K4" t="s">
-        <v>203</v>
-      </c>
       <c r="L4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N4" t="s">
         <v>52</v>
@@ -5822,7 +5822,7 @@
         <v>23</v>
       </c>
       <c r="V4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W4" t="s">
         <v>23</v>
@@ -5847,27 +5847,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5887,7 +5887,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -5907,10 +5907,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" t="s">
         <v>210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>211</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -5973,7 +5973,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
         <v>214</v>
@@ -6196,7 +6196,7 @@
         <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6249,12 +6249,12 @@
         <v>236</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -6281,7 +6281,7 @@
         <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -724,7 +724,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:43</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule-revised.xlsx
+++ b/apps/web/public/examples/example-schedule-revised.xlsx
@@ -724,7 +724,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
